--- a/경북_교육과정_관광자원_전처리_근거자료.xlsx
+++ b/경북_교육과정_관광자원_전처리_근거자료.xlsx
@@ -280,7 +280,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>생성일: 2026. 5. 11. 오후 10:37:00</t>
+          <t>생성일: 2026. 5. 17. 오전 9:06:54</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>시장 근거가 있어 생산·소비·교류가 실제 지역에서 어떻게 나타나는지 조사하는 활동과 연결됩니다.</t>
+          <t>영천공설시장, 공설시장 근거가 있어 생산·소비·교류가 실제 지역에서 어떻게 나타나는지 조사하는 활동과 연결됩니다.</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>서원, 조선, 역사·국가유산 근거가 있어 장소에 남아 있는 유물, 기록, 국가유산 또는 근현대 변화의 의미를 조사하는 활동과 연결됩니다.</t>
+          <t>서원, 향교, 문화유산 근거가 있어 장소에 남아 있는 유물, 기록, 국가유산 또는 근현대 변화의 의미를 조사하는 활동과 연결됩니다.</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>도산서원, 서원, 조선 근거가 있어 [6사05-01]의 조선 시대 유교 문화가 생활에 미친 영향 파악과 직접 연결됩니다.</t>
+          <t>도산서원, 서원, 향교 근거가 있어 [6사05-01]의 조선 시대 유교 문화가 생활에 미친 영향 파악과 직접 연결됩니다.</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>신돌석, 항일·독립운동, 독립운동·전쟁 자료 근거가 있어 [6사06-01]의 일제 식민 통치와 저항이 사회와 생활에 미친 영향 이해와 직접 연결됩니다. 국사편찬위원회 일제감시대상인물카드와 함께 지역 인물·사건을 검증할 수 있습니다.</t>
+          <t>신돌석, 독립운동, 항일·독립운동 근거가 있어 [6사06-01]의 일제 식민 통치와 저항이 사회와 생활에 미친 영향 이해와 직접 연결됩니다. 국사편찬위원회 일제감시대상인물카드와 함께 지역 인물·사건을 검증할 수 있습니다.</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>전망대, 공원, 지질공원, 수목원, 산, 강, 하천, 해안, 생태공원</t>
+          <t>전망대, 공원, 지질공원, 수목원, 산, 강, 하천, 해안, 생태공원, 기상과학관, 기상대</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>전망대, 공원, 지질공원, 산, 강, 해안, 생태공원</t>
+          <t>전망대, 공원, 지질공원, 산, 강, 해안, 생태공원, 기상과학관</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1615,17 +1615,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>전통시장, 시장, 공방, 체험장, 특산물, 항구, 역, 농촌체험, 산업관</t>
+          <t>서문시장, 칠성시장, 죽도시장, 대구약령시, 중앙시장, 공설시장, 상설시장, 항구, 항만, 산업관, 산업단지, 포항제철, 동대구역, 포항역, 김천구미역</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>전통시장, 공방, 체험장, 항구, 철도역, 농촌체험, 산업관</t>
+          <t>대표시장, 전통시장, 항구, 항만, 철도역, 산업관, 산업단지</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>경제활동, 생산, 소비, 선택, 희소성, 시장, 전통시장, 체험장, 공방, 특산물, 지역 간 교류, 생산물, 항구, 역, 농촌체험, 산업, 물류</t>
+          <t>경제활동, 생산, 소비, 선택, 희소성, 시장, 대표시장, 서문시장, 칠성시장, 죽도시장, 지역 간 교류, 생산물, 항구, 항만, 철도역, 산업, 산업단지, 물류, 포항제철, 동대구역</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1715,17 +1715,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>마을, 안전체험, 생태공원, 공원, 행정, 축제, 문화관, 체험마을, 관광, 전통시장</t>
+          <t>마을, 안전체험, 생태공원, 공원, 행정, 축제, 문화관, 관광명소, 박물관, 전망대</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>마을, 공원, 생태공원, 안전체험, 축제, 문화관, 체험마을, 전통시장</t>
+          <t>마을, 공원, 생태공원, 안전체험, 축제, 문화관, 박물관, 관광명소</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>지역문제, 환경, 안전, 교통, 주민 참여, 마을, 행정, 공원, 생태공원, 지역 알리기, 축제, 자연환경, 역사, 문화, 생산물, 관광, 체험마을, 문화관</t>
+          <t>지역문제, 환경, 안전, 교통, 주민 참여, 마을, 행정, 공원, 생태공원, 지역 알리기, 축제, 자연환경, 역사, 문화, 대표 장소, 관광, 문화관</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1815,17 +1815,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>지질공원, 주상절리, 계곡, 폭포, 산, 해안, 독도, 울릉, 독도박물관, 전망대</t>
+          <t>국립공원, 도립공원, 팔공산, 주왕산, 소백산, 가야산, 문경새재도립공원, 청량산도립공원, 금오산도립공원, 지질공원, 주상절리, 계곡, 폭포, 산, 해안, 해수욕장, 갯벌, 영일대해수욕장, 고래불해수욕장, 망양정해수욕장, 독도, 울릉, 독도박물관, 전망대</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>지질공원, 계곡, 폭포, 산, 해안, 독도, 울릉, 박물관, 전망대</t>
+          <t>국립공원, 도립공원, 지질공원, 계곡, 폭포, 산, 해안, 해수욕장, 갯벌, 독도, 울릉, 박물관, 전망대</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>산지, 하천, 해안, 지형, 주상절리, 지질공원, 계곡, 폭포, 국립공원, 도립공원, 독도, 울릉도, 영토, 해양, 동식물, 기후, 역사 기록, 독도박물관</t>
+          <t>산지, 하천, 해안, 해안선, 해안 지역, 해수욕장, 갯벌, 지형 이용, 주상절리, 지질공원, 계곡, 폭포, 국립공원, 도립공원, 팔공산, 주왕산, 소백산, 가야산, 독도, 울릉도, 영토, 해양, 동식물, 기후, 역사 기록, 독도박물관</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>안전체험, 댐, 하천, 생태공원, 해안, 도시, 전통시장, 문화관, 박물관, 교통</t>
+          <t>기상과학관, 국립대구기상과학관, 기상청, 기상대, 안전체험, 댐, 하천, 생태공원, 해안, 도시, 전통시장, 문화관, 박물관, 교통</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>안전체험, 댐, 하천, 생태공원, 해안, 전통시장, 문화관, 박물관, 도시, 교통</t>
+          <t>기상과학관, 안전체험, 댐, 하천, 생태공원, 해안, 전통시장, 문화관, 박물관, 도시, 교통</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>기후, 기온, 강수량, 자연재해, 기후변화, 하천, 댐, 해안, 안전체험, 생태, 인구, 수도권 집중, 고령화, 지역 경제, 교통 시설, 의료 시설, 문화 시설, 도시, 시장</t>
+          <t>기후, 기온, 강수량, 자연재해, 기후변화, 기상과학관, 기상청, 기상대, 하천, 댐, 해안, 안전체험, 생태, 인구, 수도권 집중, 고령화, 지역 경제, 교통 시설, 의료 시설, 문화 시설, 도시, 시장</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>경상북도독립운동기념관, 임청각, 청송 항일의병기념공원, 박열의사기념관, 왕산 허위, 신돌석장군 생가 및 유적지, 신돌석, 일제감시대상인물카드, 독립운동, 칠곡호국평화기념관, 다부동전적기념관, 영덕 장사상륙작전 전승기념관, 호국평화, 전적기념관, 6.25 전쟁</t>
+          <t>경상북도독립운동기념관, 임청각, 청송 항일의병기념공원, 박열의사기념관, 왕산 허위, 남자현지사역사공원, 신돌석장군 생가 및 유적지, 신돌석, 일제감시대상인물카드, 독립운동, 칠곡호국평화기념관, 다부동전적기념관, 영덕 장사상륙작전 전승기념관, 호국평화, 전적기념관, 6.25 전쟁</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>일제, 식민 통치, 독립운동, 항일, 의병, 감시대상인물카드, 임청각, 박열, 왕산 허위, 신돌석, 경상북도독립운동기념관, 청송 항일의병, 광복, 6·25 전쟁, 전쟁, 호국, 전적지, 피란, 생활 변화, 칠곡호국평화기념관, 장사상륙작전, 다부동전투</t>
+          <t>일제, 식민 통치, 독립운동, 항일, 의병, 감시대상인물카드, 임청각, 박열, 왕산 허위, 남자현, 신돌석, 경상북도독립운동기념관, 청송 항일의병, 광복, 6·25 전쟁, 전쟁, 호국, 전적지, 피란, 생활 변화, 칠곡호국평화기념관, 장사상륙작전, 다부동전투</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>산, 강, 하천, 해안, 전망대, 생태공원</t>
+          <t>산, 강, 하천, 해안, 전망대, 생태공원, 기상과학관, 기상대</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>산, 강, 해안, 생태공원, 전망대</t>
+          <t>산, 강, 해안, 생태공원, 전망대, 기상과학관</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>가격·품질·필요 비교, 시장 관찰, 합리적 선택 기준 세우기</t>
+          <t>가격·품질·필요 비교, 대표 시장 관찰, 합리적 선택 기준 세우기</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -3234,17 +3234,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>경제활동, 생산, 소비, 선택, 희소성, 시장, 전통시장, 체험장, 공방, 특산물</t>
+          <t>경제활동, 생산, 소비, 선택, 희소성, 시장, 대표시장, 서문시장, 칠성시장, 죽도시장</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>전통시장, 시장, 공방, 체험장, 특산물</t>
+          <t>서문시장, 칠성시장, 죽도시장, 대구약령시, 중앙시장, 공설시장, 상설시장</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>전통시장, 공방, 체험장</t>
+          <t>대표시장, 전통시장</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>생산물 이동 경로 추적, 시장·항구·역 역할 조사, 교류 지도 만들기</t>
+          <t>생산물 이동 경로 추적, 대표 시장·항만·철도역 역할 조사, 교류 지도 만들기</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3296,17 +3296,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>지역 간 교류, 생산물, 시장, 항구, 역, 농촌체험, 산업, 특산물, 물류</t>
+          <t>지역 간 교류, 생산물, 대표시장, 항구, 항만, 철도역, 산업, 산업단지, 물류, 포항제철, 동대구역</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>전통시장, 항구, 역, 농촌체험, 산업관, 특산물</t>
+          <t>서문시장, 죽도시장, 항구, 항만, 산업관, 산업단지, 포항제철, 동대구역, 포항역, 김천구미역</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>전통시장, 항구, 철도역, 농촌체험, 산업관</t>
+          <t>대표시장, 항구, 항만, 철도역, 산업관, 산업단지</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>지역의 자연환경, 역사, 문화, 생산물을 조사하고 지역을 알리는 활동에 참여한다.</t>
+          <t>지역의 자연환경, 역사, 문화, 대표 자원을 조사하고 지역을 알리는 활동에 참여한다.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>지역 홍보 카드뉴스, 축제·특산물 조사, 관광 안내 문구 만들기</t>
+          <t>지역 홍보 카드뉴스, 대표 장소 조사, 관광 안내 문구 만들기</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3544,17 +3544,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>지역 알리기, 축제, 자연환경, 역사, 문화, 생산물, 관광, 체험마을, 문화관</t>
+          <t>지역 알리기, 축제, 자연환경, 역사, 문화, 대표 장소, 관광, 문화관</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>축제, 문화관, 체험마을, 관광, 전통시장</t>
+          <t>축제, 문화관, 관광명소, 박물관, 전망대</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>축제, 문화관, 체험마을, 전통시장</t>
+          <t>축제, 문화관, 박물관, 관광명소</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -3725,22 +3725,22 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>산지, 하천, 해안, 지형 분포</t>
+          <t>산지, 하천, 해안, 지형 분포와 이용</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>산지, 하천, 해안, 지형, 주상절리, 지질공원, 계곡, 폭포, 국립공원, 도립공원</t>
+          <t>산지, 하천, 해안, 해안선, 해안 지역, 해수욕장, 갯벌, 지형 이용, 주상절리, 지질공원, 계곡, 폭포, 국립공원, 도립공원, 팔공산, 주왕산, 소백산, 가야산</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>지질공원, 주상절리, 계곡, 폭포, 산, 해안</t>
+          <t>국립공원, 도립공원, 팔공산, 주왕산, 소백산, 가야산, 문경새재도립공원, 청량산도립공원, 금오산도립공원, 지질공원, 주상절리, 계곡, 폭포, 산, 해안, 해수욕장, 갯벌, 영일대해수욕장, 고래불해수욕장, 망양정해수욕장</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>지질공원, 계곡, 폭포, 산, 해안</t>
+          <t>국립공원, 도립공원, 지질공원, 계곡, 폭포, 산, 해안, 해수욕장, 갯벌</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3854,17 +3854,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>기후, 기온, 강수량, 자연재해, 기후변화, 하천, 댐, 해안, 안전체험, 생태</t>
+          <t>기후, 기온, 강수량, 자연재해, 기후변화, 기상과학관, 기상청, 기상대, 하천, 댐, 해안, 안전체험, 생태</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>안전체험, 댐, 하천, 생태공원, 해안</t>
+          <t>기상과학관, 국립대구기상과학관, 기상청, 기상대, 안전체험, 댐, 하천, 생태공원, 해안</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>안전체험, 댐, 하천, 생태공원, 해안</t>
+          <t>기상과학관, 안전체험, 댐, 하천, 생태공원, 해안</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>국사편찬위원회 일제감시대상인물카드 키워드와 경북 독립운동 장소를 연결해 인물·사건 타임라인 만들기</t>
+          <t>국사편찬위원회 일제감시대상인물카드 키워드와 대구·경북 독립운동 장소를 연결해 인물·사건 타임라인 만들기</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>일제, 식민 통치, 독립운동, 항일, 의병, 감시대상인물카드, 임청각, 박열, 왕산 허위, 신돌석, 경상북도독립운동기념관, 청송 항일의병</t>
+          <t>일제, 식민 통치, 독립운동, 항일, 의병, 감시대상인물카드, 임청각, 박열, 왕산 허위, 남자현, 신돌석, 경상북도독립운동기념관, 청송 항일의병</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>경상북도독립운동기념관, 임청각, 청송 항일의병기념공원, 박열의사기념관, 왕산 허위, 신돌석장군 생가 및 유적지, 신돌석, 일제감시대상인물카드, 독립운동</t>
+          <t>경상북도독립운동기념관, 임청각, 청송 항일의병기념공원, 박열의사기념관, 왕산 허위, 남자현지사역사공원, 신돌석장군 생가 및 유적지, 신돌석, 일제감시대상인물카드, 독립운동</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -5479,17 +5479,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>전통시장, 시장, 오일장, 장터, 공방, 체험장, 특산물, 항구, 철도역, 역, 산업관, 농촌체험, 물류</t>
+          <t>서문시장, 칠성시장, 죽도시장, 대구약령시, 안동구시장, 안동중앙신시장, 경주중앙시장, 성동시장, 영천공설시장, 구미새마을중앙시장, 구미중앙시장, 김천황금시장, 김천평화시장, 영주365시장, 영주종합시장, 상주중앙시장, 문경중앙시장, 예천상설시장, 봉화상설시장, 의성전통시장, 청도시장, 고령대가야시장, 왜관시장, 울진바지게시장, 영덕시장, 중앙시장, 공설시장, 상설시장, 종합시장, 포항제철, 포스코, 산업관, 산업단지, 국가산업단지, 항만, 포항항, 영일만항, 구룡포항, 강구항, 후포항, 동대구역, 서대구역, 대구역, 포항역, 김천구미역, 신경주역, 안동역, 영주역, 점촌역, 영천역, 대구국제공항, 복합환승센터</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>생산, 소비, 교류, 산업, 공장, 농촌, 가격, 상품</t>
+          <t>생산, 소비, 교류, 산업, 공장, 가격, 상품, 항만, 철도, 공항</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>/서원|향교|사찰|고택|종택|왕릉|고분|성곽|지질공원|수목원/</t>
+          <t>/서원|향교|사찰|고택|종택|왕릉|고분|성곽|지질공원|수목원|오일장|장터|공방|체험장|농촌체험|어촌체험|특산물|농산물|수산물/</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>/시장|공방|체험장|상품|가격|소비|생산/ -&gt; /경제활동|선택/ / /항구|역|교류|물류|특산|농촌|산업/ -&gt; /교류/</t>
+          <t>/서문시장|칠성시장|죽도시장|약령시|중앙시장|공설시장|상설시장|종합시장|가격|소비|상품/ -&gt; /경제활동|선택/ / /항구|항만|철도역|동대구역|포항역|물류|산업|포항제철|포스코|공항/ -&gt; /교류/</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>독도, 울릉, 지질공원, 주상절리, 해안, 해양, 계곡, 폭포, 국립공원, 도립공원</t>
+          <t>독도, 울릉, 지질공원, 주상절리, 해안, 해안선, 해수욕장, 갯벌, 사구, 해양, 계곡, 폭포, 국립공원, 도립공원, 팔공산, 주왕산, 소백산, 가야산, 문경새재, 청량산, 금오산</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>산지, 하천, 강, 영토, 섬, 전망대, 자연생태, 생태, 동식물</t>
+          <t>산지, 하천, 강, 영토, 섬, 전망대, 자연생태, 생태, 동식물, 해안 지역, 지형 이용, 바닷가, 모래, 파도, 탐방로</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>/독도|울릉/ -&gt; /독도/ / /./ -&gt; /지형/</t>
+          <t>/독도|울릉/ -&gt; /독도/ / /해안|해수욕장|갯벌|사구|바닷가|해양/ -&gt; /지형/ / /국립공원|도립공원|팔공산|주왕산|소백산|가야산|문경새재|청량산|금오산|산지/ -&gt; /지형/ / /./ -&gt; /지형/</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>/지질공원|수목원|식물원|계곡|폭포|해수욕장|전통시장|공방|산업관|안전체험|생가|독립|의병|항일|일제|식민|신돌석|임청각|박열|왕산|허위|호국|전쟁|전적|근대/</t>
+          <t>/지질공원|수목원|식물원|계곡|폭포|해수욕장|전통시장|공방|산업관|안전체험|생가|독립|의병|항일|일제|식민|신돌석|임청각|박열|왕산\s*허위|왕산허위|허위|호국|전쟁|전적|근대/</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>신돌석, 독립운동, 항일, 의병, 임청각, 박열, 왕산, 허위, 청송 항일, 감시대상인물, 일제, 식민, 광복, 장사상륙, 다부동, 칠곡호국, 호국평화, 6.25, 6·25, 전쟁, 전적</t>
+          <t>신돌석, 남자현, 남자현지사, 독립운동, 항일, 의병, 임청각, 박열, 왕산 허위, 왕산허위, 청송 항일, 감시대상인물, 일제, 식민, 광복, 장사상륙, 다부동, 칠곡호국, 호국평화, 6.25, 6·25, 전쟁, 전적</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>/신돌석|독립|항일|의병|임청각|박열|왕산|허위|일제|식민|감시대상/ -&gt; /식민|저항/ / /광복|6\.25|6·25|전쟁|호국|장사상륙|다부동|칠곡|전적|평화/ -&gt; /광복|전쟁/</t>
+          <t>/신돌석|남자현|독립|항일|의병|임청각|박열|왕산\s*허위|왕산허위|허위|일제|식민|감시대상/ -&gt; /식민|저항/ / /광복|6\.25|6·25|전쟁|호국|장사상륙|다부동|칠곡|전적|평화/ -&gt; /광복|전쟁/</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -6301,11 +6301,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>문화·지역 알리기</t>
+          <t>세계 지리·국가 이해</t>
         </is>
       </c>
       <c r="E20">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -6319,17 +6319,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>축제, 민속촌, 전통마을, 체험마을, 문화관, 문화원, 세계문화, 다문화, 국제, 박물관, 미디어, 기록관, 전망대, 과학관, 천문대</t>
+          <t>지구본, 세계지도, 세계 지도, 위도, 경도, 대륙, 대양, 세계문화, 세계 문화, 다문화, 국제, 천문대, 우주, 과학관</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>문화, 민속, 세계, 대륙, 대양, 지역 알리기, 관광, 홍보, 스마트, 고령화</t>
+          <t>공간 자료, 지도, 여러 나라, 나라별, 세계 각국, 외국, 문화관, 박물관, 민속, 교류, 전망대</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t/>
+          <t>/농촌|어촌|체험마을|농어촌|생산|소비|수확|갯벌|어업|특산|전통시장|오일장|장터|지역축제|지역 알리기|관광명소|자연생태|숲|하천|해안|산지|탐방로|등산로|서원|향교|고택|종택|사찰|고분|국가유산|독립|호국|전쟁/</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>/세계|국제|대륙|대양|다문화/ -&gt; /세계|다양한 문화/ / /축제|관광|홍보|지역 알리기/ -&gt; /지역을 알리/ / /미디어|기록관|뉴스|방송/ -&gt; /미디어/</t>
+          <t>/지구본|세계\s*지도|위도|경도|공간 자료|천문|우주|과학관|전망대/ -&gt; /지구본|지도/ / /대륙|대양|여러 나라|나라별|세계 각국|외국|세계문화|세계 문화|국제|다문화|민속|교류/ -&gt; /대륙|대양|나라/</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -6441,22 +6441,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>자연탐구</t>
+          <t>현충·근현대사</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🌿</t>
+          <t>🎖️</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>국립·도립공원, 생태공원·습지, 수목원·식물원, 계곡·폭포, 지질공원, 해안·섬</t>
+          <t>독립운동·의병, 항일·일제강점기, 6·25·국가수호, 근대역사·민주주의</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>공원, 생태, 수목원, 식물원, 계곡, 폭포, 습지, 지질, 야생화, 자연, 산림, 강, 호수, 섬, 해안, 독도, 울릉</t>
+          <t>현충, 호국, 독립운동, 의병, 항일, 일제, 전쟁, 6·25, 6.25, 전적, 평화, 근대, 민주</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -6473,22 +6473,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>과학체험</t>
+          <t>자연·생태</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔬</t>
+          <t>🌿</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>과학관, 천문대, 자연사박물관, 지질탐사지</t>
+          <t>생태관광, 생태공원·습지, 수목원·식물원, 계곡·폭포, 지질공원, 해안·섬</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>과학관, 천문대, 자연사, 과학체험, 지질탐사</t>
+          <t>생태관광, 공원, 생태, 수목원, 식물원, 계곡, 폭포, 습지, 지질, 야생화, 자연, 산림, 강, 호수, 섬, 해안, 해안선, 해수욕장, 갯벌, 사구, 독도, 울릉</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -6505,22 +6505,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>생활체험</t>
+          <t>산지·탐방로</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🏘️</t>
+          <t>🥾</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>전통마을·민속촌, 농촌체험, 공예·도자기, 전통시장</t>
+          <t>국립공원 탐방로, 산림청 등산로, 산지·지형 관찰, 탐방 안전</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>전통마을, 체험마을, 민속촌, 농촌, 한옥마을, 공예, 시장, 오일장, 도자기</t>
+          <t>탐방로, 등산로, 국립공원, 도립공원, 산림청, 산지, 난이도, 코스, 탐방, 산, 팔공산, 주왕산, 소백산, 가야산, 문경새재, 청량산, 금오산</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -6537,22 +6537,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>인물역사</t>
+          <t>공원·생활환경</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>👤</t>
+          <t>🏞️</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>생가, 독립운동 유적, 기념관, 근현대 역사</t>
+          <t>근린·생활공원, 수변·생태공원, 문화·역사공원, 공공시설 탐구</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>생가, 독립운동, 의병, 기념관, 항일, 역사, 역사관, 문화관, 삼성현, 근대</t>
+          <t>근린공원, 도시공원, 수변공원, 생태공원, 생활환경, 공공시설, 공원, 야외무대, 체육공원</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -6564,160 +6564,160 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>소분류</t>
+          <t>대분류</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>사찰·불교문화</t>
+          <t>대표 경제거점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t/>
+          <t>🏭</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t/>
+          <t>대표 시장, 산업·물류 거점, 항만·철도 거점</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>사찰, 절, 암자, 불국사, 석굴암</t>
+          <t>서문시장, 칠성시장, 죽도시장, 대구약령시, 중앙시장, 공설시장, 상설시장, 포항제철, 포스코, 산업관, 산업단지, 항구, 항만, 철도역, 동대구역, 포항역, 대구국제공항, 물류</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+          <t>장소명과 주소를 기반으로 앱의 관광자원 대분류를 부여</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>소분류</t>
+          <t>대분류</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>서원·향교</t>
+          <t>지역축제</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t/>
+          <t>🎪</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t/>
+          <t>전통문화축제, 생태·자연축제, 예술·공연축제, 전년도 참고</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>서원, 향교, 서당</t>
+          <t>축제, 행사, 문화제, 예술제, 페스티벌, 전통, 계절</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+          <t>장소명과 주소를 기반으로 앱의 관광자원 대분류를 부여</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>소분류</t>
+          <t>대분류</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>왕릉·고분</t>
+          <t>박물관·전시</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t/>
+          <t>🏛️</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t/>
+          <t>역사·문화박물관, 과학·자연사전시, 미술관·전시관, 농업·생활사전시</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>왕릉, 고분, 능</t>
+          <t>박물관, 미술관, 전시관, 전시, 역사관, 문화관, 기념관, 자연사, 과학관, 유물</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+          <t>장소명과 주소를 기반으로 앱의 관광자원 대분류를 부여</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>소분류</t>
+          <t>대분류</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>유적·사적지</t>
+          <t>관광명소</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t/>
+          <t>🧭</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t/>
+          <t>역사·문화 관광지, 자연경관 관광지, 지역생활 관광지, 보조 관광자료</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>사적, 유적, 유적지</t>
+          <t>관광지, 관광명소, 명소, 전망대, 둘레길, 마을, 문화관광, 자연경관, 계곡, 강, 바다, 역사</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+          <t>장소명과 주소를 기반으로 앱의 관광자원 대분류를 부여</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>소분류</t>
+          <t>대분류</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>성곽·읍성</t>
+          <t>과학체험</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t/>
+          <t>🔬</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t/>
+          <t>과학관, 천문대, 자연사박물관, 지질탐사지</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>성곽, 읍성, 산성</t>
+          <t>과학관, 천문대, 천문과학관, 천체관측, 천체투영관, 별빛, 우주, 자연사, 과학체험, 지질탐사</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+          <t>장소명과 주소를 기반으로 앱의 관광자원 대분류를 부여</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>종택·고택</t>
+          <t>사찰·불교문화</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>종택, 고택</t>
+          <t>사찰, 절, 암자, 불국사, 석굴암</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>국립·도립공원</t>
+          <t>서원·향교</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>국립공원, 도립공원</t>
+          <t>서원, 향교, 서당</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>생태공원·습지</t>
+          <t>왕릉·고분</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>생태공원, 습지, 생태원</t>
+          <t>왕릉, 고분, 능</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>수목원·식물원</t>
+          <t>유적·사적지</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>수목원, 식물원</t>
+          <t>사적, 유적, 유적지</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>계곡·폭포</t>
+          <t>성곽·읍성</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>계곡, 폭포</t>
+          <t>성곽, 읍성, 산성</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>지질공원</t>
+          <t>종택·고택</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>지질공원, 지질</t>
+          <t>종택, 고택</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>해안·섬</t>
+          <t>독립운동·의병</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>해안, 섬, 독도, 울릉</t>
+          <t>독립운동, 의병, 항일, 생가</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>과학관</t>
+          <t>항일·일제강점기</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>과학관, 과학체험</t>
+          <t>일제, 식민, 항일, 감시대상</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>천문대</t>
+          <t>6·25·국가수호</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -7000,7 +7000,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>천문대, 천문, 별빛, 반딧불</t>
+          <t>6·25, 6.25, 전쟁, 호국, 전적, 국가수호</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>자연사박물관</t>
+          <t>근대역사·민주주의</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>자연사</t>
+          <t>근대, 민주, 평화, 역사관</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>지질탐사지</t>
+          <t>생태관광</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>암석, 지층, 화산</t>
+          <t>생태관광, 성류굴</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>전통마을·민속촌</t>
+          <t>생태공원·습지</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>전통마을, 민속촌, 한옥마을, 체험마을</t>
+          <t>생태공원, 습지, 생태원</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>농촌체험</t>
+          <t>수목원·식물원</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>농촌, 농업, 농장</t>
+          <t>수목원, 식물원</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>공예·도자기</t>
+          <t>계곡·폭포</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>공예, 도자기, 공방</t>
+          <t>계곡, 폭포</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>전통시장</t>
+          <t>지질공원</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>시장, 오일장, 장터</t>
+          <t>지질공원, 지질</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -7209,7 +7209,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>생가</t>
+          <t>해안·섬</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>생가</t>
+          <t>해안, 해안선, 해수욕장, 갯벌, 사구, 섬, 독도, 울릉</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>독립운동 유적</t>
+          <t>국립공원 탐방로</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>독립운동, 항일, 의병</t>
+          <t>국립공원 탐방로, 탐방로</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>기념관</t>
+          <t>산림청 등산로</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>기념관, 문화관</t>
+          <t>산림청 등산로, 등산로</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -7305,32 +7305,1024 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>산지·지형 관찰</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>산지, 지형, 산, 국립공원, 도립공원, 팔공산, 주왕산, 소백산, 가야산, 문경새재, 청량산, 금오산</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>탐방 안전</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>통제, 난이도, 탐방가능구간</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>근린·생활공원</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>근린공원, 생활공원, 도시공원</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>수변·생태공원</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>수변공원, 생태공원</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>문화·역사공원</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>문화, 역사, 현충, 기념</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>공공시설 탐구</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>공공시설, 체육공원, 야외무대</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>대표 시장</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>서문시장, 칠성시장, 죽도시장, 대구약령시, 중앙시장, 공설시장, 상설시장, 종합시장</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>산업·물류 거점</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>산업관, 산업단지, 포항제철, 포스코, 물류, 대구국제공항</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>항만·철도 거점</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>항구, 항만, 철도역, 동대구역, 포항역, 김천구미역, 신경주역, 안동역, 영주역</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>전통문화축제</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>전통, 문화제, 민속, 축제</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>생태·자연축제</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>생태, 자연, 꽃, 숲, 환경</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>예술·공연축제</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>예술, 공연, 음악, 연극</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>전년도 참고</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>전년도, 작년, 종료</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>역사·문화 관광지</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>역사, 문화, 유적, 전통, 마을</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>자연경관 관광지</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>자연경관, 계곡, 강, 바다, 해안, 산, 숲, 전망</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>지역생활 관광지</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>지역, 마을, 시장, 생활, 교류</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>보조 관광자료</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>관광지, 관광명소, 보조자료</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>역사·문화박물관</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>역사, 문화, 유물, 생활사</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>과학·자연사전시</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>과학, 자연사, 생태, 천문</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>미술관·전시관</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>미술관, 전시관, 전시</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>농업·생활사전시</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>농업, 생활사, 민속</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>과학관</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>과학관, 과학체험</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>천문대</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>천문대, 천문과학관, 천체관측, 천체투영관, 천문, 별빛, 우주, 반딧불</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>자연사박물관</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>자연사</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>지질탐사지</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>암석, 지층, 화산</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>전통마을·민속촌</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>전통마을, 민속촌, 한옥마을, 체험마을</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>공예·도자기</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>공예, 도자기</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>전통시장</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>시장, 서문시장, 칠성시장, 죽도시장, 대구약령시</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>생가</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>생가</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>독립운동 유적</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>독립운동, 항일, 의병</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>기념관</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>기념관, 문화관</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>소분류</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>근현대 역사</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
         <is>
           <t>근대, 역사, 역사관</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>장소명과 주소를 기반으로 세부 장소유형을 부여</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F30"/>
+  <autoFilter ref="A1:F61"/>
 </worksheet>
 </file>
 
@@ -8093,7 +9085,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>대릉원 · 천마총 · 고대 · 역사 원자료·고대/고려</t>
+          <t>지도·위치 · 자료 조사 · 현장 관찰 · 역사 자료 · 이동·통신 · 대릉원</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -8204,7 +9196,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>항일·독립운동 · 역사 원자료·고대/고려</t>
+          <t>지도·위치 · 자료 조사 · 현장 관찰 · 역사 자료 · 이동·통신 · 항일·독립운동</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -8315,7 +9307,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>신돌석 · 항일·독립운동 · 독립운동·전쟁 자료</t>
+          <t>지도·위치 · 자료 조사 · 역사 자료 · 천체 관측 · 이동·통신 · 신돌석</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -8409,7 +9401,7 @@
         <v>26.5</v>
       </c>
       <c r="R5">
-        <v>178</v>
+        <v>235</v>
       </c>
       <c r="S5">
         <v>30</v>
@@ -8426,12 +9418,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>도산서원 · 서원 · 조선 · 조선·근대 생활사</t>
+          <t>지도·위치 · 지역 특성 · 자료 조사 · 비교하기 · 역사 자료 · 천체 관측</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>도산서원, 서원, 조선 근거가 있어 [6사05-01]의 조선 시대 유교 문화가 생활에 미친 영향 파악과 직접 연결됩니다.</t>
+          <t>도산서원, 서원, 향교 근거가 있어 [6사05-01]의 조선 시대 유교 문화가 생활에 미친 영향 파악과 직접 연결됩니다.</t>
         </is>
       </c>
     </row>
@@ -8513,7 +9505,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>천문대</t>
+          <t>문화·역사공원</t>
         </is>
       </c>
       <c r="Q6">
@@ -8537,7 +9529,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>우리나라 지형 여행 · 우리 땅 독도</t>
+          <t>국토 지형 · 지도·위치 · 지역 특성 · 자료 조사 · 이동·통신 · 산지</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -8648,7 +9640,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>불국사 · 고대</t>
+          <t>지도·위치 · 자료 조사 · 현장 관찰 · 역사 자료 · 이동·통신 · 불국사</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
